--- a/Casos_de_Prueba_ElMirador_final.xlsx
+++ b/Casos_de_Prueba_ElMirador_final.xlsx
@@ -2316,8 +2316,8 @@
     <mergeCell ref="B12:K12"/>
     <mergeCell ref="B11:K11"/>
     <mergeCell ref="A8:K8"/>
+    <mergeCell ref="B49:L49"/>
     <mergeCell ref="A48:L48"/>
-    <mergeCell ref="B49:L49"/>
     <mergeCell ref="B14:K14"/>
     <mergeCell ref="B17:K17"/>
     <mergeCell ref="B13:K13"/>
